--- a/data-raw/fsaArcPlc/input_data/fsaMyaPrice/MYA_2024.xlsx
+++ b/data-raw/fsaArcPlc/input_data/fsaMyaPrice/MYA_2024.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\EPAS\2014FBIMP\ARC_PLC\Webpage Posting\2025-0410\Program Year 2024\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\EPAS\2014FBIMP\ARC_PLC\Webpage Posting\2025-0812\Program Year 2024\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D76413D2-11B6-4C41-B983-DEEB39E477E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40BA0519-B10B-426F-877C-E037E611E2F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,12 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="55">
   <si>
     <t>TABLE 1. 2018/19-2024/25 MARKET YEAR AVERAGE (MYA) PRICES</t>
   </si>
   <si>
-    <t>April 10, 2025 1/</t>
+    <t>August 12, 2025 1/</t>
   </si>
   <si>
     <t>Commodity</t>
@@ -73,25 +73,28 @@
     <t>Bushel</t>
   </si>
   <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Barley</t>
+  </si>
+  <si>
+    <t>Oats</t>
+  </si>
+  <si>
+    <t>Peanuts</t>
+  </si>
+  <si>
+    <t>Aug. 1-Jul. 31</t>
+  </si>
+  <si>
+    <t>August 29, 2025</t>
+  </si>
+  <si>
+    <t>Pound</t>
+  </si>
+  <si>
     <t>P</t>
-  </si>
-  <si>
-    <t>Barley</t>
-  </si>
-  <si>
-    <t>Oats</t>
-  </si>
-  <si>
-    <t>Peanuts</t>
-  </si>
-  <si>
-    <t>Aug. 1-Jul. 31</t>
-  </si>
-  <si>
-    <t>August 29, 2025</t>
-  </si>
-  <si>
-    <t>Pound</t>
   </si>
   <si>
     <t>Corn</t>
@@ -203,19 +206,16 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -692,7 +692,7 @@
         <v>6.96</v>
       </c>
       <c r="K5" s="6">
-        <v>5.5</v>
+        <v>5.52</v>
       </c>
       <c r="L5" s="8" t="s">
         <v>17</v>
@@ -730,7 +730,7 @@
         <v>7.39</v>
       </c>
       <c r="K6" s="6">
-        <v>6.5</v>
+        <v>6.31</v>
       </c>
       <c r="L6" s="8" t="s">
         <v>17</v>
@@ -768,7 +768,7 @@
         <v>3.92</v>
       </c>
       <c r="K7" s="6">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L7" s="8" t="s">
         <v>17</v>
@@ -806,21 +806,21 @@
         <v>0.26900000000000002</v>
       </c>
       <c r="K8" s="10">
-        <v>0.255</v>
+        <v>0.25900000000000001</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>16</v>
@@ -844,21 +844,21 @@
         <v>4.55</v>
       </c>
       <c r="K9" s="6">
-        <v>4.3499999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>26</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>16</v>
@@ -885,18 +885,18 @@
         <v>4.0999999999999996</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>16</v>
@@ -920,21 +920,21 @@
         <v>12.4</v>
       </c>
       <c r="K11" s="6">
-        <v>9.9499999999999993</v>
+        <v>10</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>23</v>
@@ -958,7 +958,7 @@
         <v>0.152</v>
       </c>
       <c r="K12" s="10">
-        <v>0.13800000000000001</v>
+        <v>0.13600000000000001</v>
       </c>
       <c r="L12" s="8" t="s">
         <v>17</v>
@@ -966,13 +966,13 @@
     </row>
     <row r="13" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>31</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>23</v>
@@ -996,7 +996,7 @@
         <v>0.40400000000000003</v>
       </c>
       <c r="K13" s="10">
-        <v>0.34799999999999998</v>
+        <v>0.35899999999999999</v>
       </c>
       <c r="L13" s="8" t="s">
         <v>17</v>
@@ -1004,13 +1004,13 @@
     </row>
     <row r="14" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>23</v>
@@ -1034,7 +1034,7 @@
         <v>0.24299999999999999</v>
       </c>
       <c r="K14" s="10">
-        <v>0.19900000000000001</v>
+        <v>0.20200000000000001</v>
       </c>
       <c r="L14" s="8" t="s">
         <v>17</v>
@@ -1042,13 +1042,13 @@
     </row>
     <row r="15" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>23</v>
@@ -1072,21 +1072,21 @@
         <v>0.36899999999999999</v>
       </c>
       <c r="K15" s="10">
-        <v>0.33</v>
+        <v>0.33900000000000002</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>23</v>
@@ -1110,21 +1110,21 @@
         <v>0.35699999999999998</v>
       </c>
       <c r="K16" s="10">
-        <v>0.26</v>
+        <v>0.26400000000000001</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>23</v>
@@ -1148,21 +1148,21 @@
         <v>0.21199999999999999</v>
       </c>
       <c r="K17" s="10">
-        <v>0.2155</v>
+        <v>0.23300000000000001</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>16</v>
@@ -1186,7 +1186,7 @@
         <v>12.1</v>
       </c>
       <c r="K18" s="10">
-        <v>12.3</v>
+        <v>12.5</v>
       </c>
       <c r="L18" s="8" t="s">
         <v>17</v>
@@ -1194,13 +1194,13 @@
     </row>
     <row r="19" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>23</v>
@@ -1224,21 +1224,21 @@
         <v>0.57899999999999996</v>
       </c>
       <c r="K19" s="10">
-        <v>0.48249999999999998</v>
+        <v>0.45</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>23</v>
@@ -1262,7 +1262,7 @@
         <v>0.2</v>
       </c>
       <c r="K20" s="10">
-        <v>0.2</v>
+        <v>0.32800000000000001</v>
       </c>
       <c r="L20" s="8" t="s">
         <v>17</v>
@@ -1270,13 +1270,13 @@
     </row>
     <row r="21" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>23</v>
@@ -1300,21 +1300,21 @@
         <v>0.36</v>
       </c>
       <c r="K21" s="10">
-        <v>0.30299999999999999</v>
+        <v>0.24299999999999999</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>23</v>
@@ -1338,21 +1338,21 @@
         <v>0.24</v>
       </c>
       <c r="K22" s="10">
-        <v>0.24</v>
+        <v>0.39400000000000002</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>23</v>
@@ -1379,18 +1379,18 @@
         <v>0.39</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>23</v>
@@ -1414,21 +1414,21 @@
         <v>0.39489999999999997</v>
       </c>
       <c r="K24" s="10">
-        <v>0.33610000000000001</v>
+        <v>0.34010000000000001</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>23</v>
@@ -1452,21 +1452,21 @@
         <v>0.159</v>
       </c>
       <c r="K25" s="10">
-        <v>0.14199999999999999</v>
+        <v>0.14099999999999999</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>23</v>
@@ -1493,18 +1493,18 @@
         <v>0.152</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>23</v>
@@ -1528,15 +1528,15 @@
         <v>0.223</v>
       </c>
       <c r="K27" s="15">
-        <v>0.22500000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="L27" s="17" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B29" s="20"/>
       <c r="C29" s="20"/>
@@ -1552,7 +1552,7 @@
     </row>
     <row r="30" spans="1:12" ht="26.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B30" s="20"/>
       <c r="C30" s="20"/>
@@ -1568,7 +1568,7 @@
     </row>
     <row r="31" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="20"/>
@@ -1584,7 +1584,7 @@
     </row>
     <row r="32" spans="1:12" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B32" s="20"/>
       <c r="C32" s="20"/>
